--- a/docs/kslt-teksty-na-podtverzhdenie.xlsx
+++ b/docs/kslt-teksty-na-podtverzhdenie.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1931,6 +1931,358 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Страница турнира — подпись круга сетки</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>js/tournament-generator.js:ROUND_DEFS</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>kg.64[0]</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>1/32 Финала</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Round of 64</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>1/32 финал</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>НОВОЕ 06.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Страница турнира — подпись круга сетки</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>js/tournament-generator.js:ROUND_DEFS</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>kg.64[1]</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>1/16 Финала</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>1/16 финал</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="8" t="n"/>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>НОВОЕ 06.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Страница турнира — подпись круга сетки</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>js/tournament-generator.js:ROUND_DEFS</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>kg.32[1]</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>1/8 Финала</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>1/8 финал</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>НОВОЕ 06.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Страница турнира — подпись круга сетки</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>js/tournament-generator.js:ROUND_DEFS</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>kg.*.QF</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Четвертьфинал</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Quarterfinal</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>Чейрек финал</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="8" t="n"/>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>НОВОЕ 06.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Страница турнира — подпись круга сетки</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>js/tournament-generator.js:ROUND_DEFS</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>kg.*.SF</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Полуфинал</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Semifinal</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>Жарым финал</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="8" t="n"/>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>НОВОЕ 06.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Страница турнира — подпись круга сетки</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>js/tournament-generator.js:ROUND_DEFS</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>kg.*.F</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Финал</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>Финал</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="8" t="n"/>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>НОВОЕ 06.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Страница турнира — раздел «Сетка», когда сетки ещё нет</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>js/tournament-detail.js:drawNotYet</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>drawNotYet</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Сетка ещё не сформирована</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>The draw has not been made yet</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Тор азырынча түзүлө элек</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>НОВОЕ 06.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Страница турнира — раздел «Сетка», подсказка под строкой</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>js/tournament-detail.js:drawNotYetHint</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>drawNotYetHint</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Она появится здесь, когда пройдёт жеребьёвка.</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>The bracket will appear here once the draw is done.</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Жеребьёвка өткөндөн кийин ал ушул жерде көрүнөт.</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="8" t="n"/>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>НОВОЕ 06.10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A5:J37"/>
   <mergeCells count="3">
